--- a/stories/arbres/ATOM-TMP.SEM.002-02.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ava est à la cuisine. Papa accroche un calendrier. Papa dit : lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Ava reste à la maison. Elle joue avec papa. Samedi, Ava reste aussi. Dimanche encore. Papa dit : samedi et dimanche, c'est le week-end. Ava touche mercredi. Elle touche samedi. Elle touche dimanche. Papa dit : mercredi, samedi, dimanche, on est à la maison.</t>
+          <t>Ava est à la cuisine. Papa accroche un calendrier. Lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Ava reste à la maison. Elle joue avec papa. Samedi, Ava reste aussi. Dimanche encore. Samedi et dimanche, c'est le week-end. Ava touche mercredi. Elle touche samedi. Elle touche dimanche. Mercredi, samedi, dimanche, on est à la maison.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Ava est à la cuisine. Papa accroche un calendrier.
+papa|Lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Ava reste à la maison. Elle joue avec papa. Samedi, Ava reste aussi. Dimanche encore.
+papa|Samedi et dimanche, c'est le week-end.
+narrateur|Ava touche mercredi. Elle touche samedi. Elle touche dimanche.
+papa|Mercredi, samedi, dimanche, on est à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Ava est à la maison le mercredi. Quels autres jours aussi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Ava a nommé mercredi. Elle a nommé samedi et dimanche. C'est le week-end.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range le calendrier. Ava dessine un soleil.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.002-02.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 papa|Mercredi, samedi, dimanche, on est à la maison.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Ava est à la maison le mercredi. Quels autres jours aussi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Ava a nommé mercredi. Elle a nommé samedi et dimanche. C'est le week-end.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Papa range le calendrier. Ava dessine un soleil.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.SEM.002-02.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ava nomme mercredi et le week-end</t>
+          <t>Le pain du samedi</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amir veut un pique-nique. Mercredi au square, le banc est mouillé. Ils essuient. Samedi, week-end, le pain et la nappe attendent dans l'herbe.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ava est à la cuisine. Papa accroche un calendrier. Lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Ava reste à la maison. Elle joue avec papa. Samedi, Ava reste aussi. Dimanche encore. Samedi et dimanche, c'est le week-end. Ava touche mercredi. Elle touche samedi. Elle touche dimanche. Mercredi, samedi, dimanche, on est à la maison.</t>
+          <t>Le gravier du square sent encore la pluie. Une flaque garde le ciel, tout petit. Les chaînes des balançoires sont froides. C'est mercredi, Amir. Pas d'école. On reste au square ? Un moment. Samedi, on fera le pique-nique. Avec le pain ? Avec le pain. Samedi, c'est le week-end. Amir pose la main sur le banc. Le bois est mouillé, luisant. Il est froid. La pluie est restée. On essuie ? Oui. Papa tend un linge de poche. En ce moment, Amir frotte le banc. L'eau part en petites traces. Tu fais une place sèche. Pour samedi. Pour samedi. Et pour maintenant. Ils s'assoient au bord. Le gravier croque sous une chaussure. Je vois une fourmi. Elle cherche aussi. Amir suit la fourmi du doigt. Elle contourne la flaque. Mercredi, on prépare. Samedi, on mange dehors. Et dimanche ? Dimanche aussi, pas d'école. Samedi et dimanche, le week-end. Un oiseau secoue une branche. Une goutte tombe dans la flaque. Ploc. Tu as entendu ? Oui, papa. Amir pose une feuille sur l'eau. Elle flotte, puis tourne. Un bateau. Il va au pique-nique. Samedi, le vrai pain. Pas la feuille. Pas la feuille. Le banc sèche un peu plus. Le linge est lourd d'eau. On le tord ? Je tords. L'eau tombe entre les graviers. Merci. Le banc est à nous. J'attends samedi. Le square sent l'herbe mouillée. Une cloche lointaine sonne deux fois.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ava est à la cuisine. Papa accroche un calendrier. Papa dit : lundi, mardi, jeudi, vendredi, c'est l'école. &lt;emphasis level="moderate"&gt;mercredi&lt;/emphasis&gt;, Ava reste à la maison. Elle joue avec papa. Samedi, Ava reste aussi. Dimanche encore. Papa dit : samedi et dimanche, c'est le week-end. Ava touche mercredi. Elle touche samedi. Elle touche dimanche. Papa dit : mercredi, samedi, dimanche, on est à la maison.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le gravier du square sent encore la pluie. Une flaque garde le ciel, tout petit. Les chaînes des balançoires sont froides. C'est mercredi, Amir. Pas d'école. On reste au square ? Un moment. Samedi, on fera le pique-nique. Avec le pain ? Avec le pain. Samedi, c'est le week-end. Amir pose la main sur le banc. Le bois est mouillé, luisant. Il est froid. La pluie est restée. On essuie ? Oui. Papa tend un linge de poche. En ce moment, Amir frotte le banc. L'eau part en petites traces. Tu fais une place sèche. Pour samedi. Pour samedi. Et pour maintenant. Ils s'assoient au bord. Le gravier croque sous une chaussure. Je vois une fourmi. Elle cherche aussi. Amir suit la fourmi du doigt. Elle contourne la flaque. Mercredi, on prépare. Samedi, on mange dehors. Et dimanche ? Dimanche aussi, pas d'école. Samedi et dimanche, le week-end. Un oiseau secoue une branche. Une goutte tombe dans la flaque. Ploc. Tu as entendu ? Oui, papa. Amir pose une feuille sur l'eau. Elle flotte, puis tourne. Un bateau. Il va au pique-nique. Samedi, le vrai pain. Pas la feuille. Pas la feuille. Le banc sèche un peu plus. Le linge est lourd d'eau. On le tord ? Je tords. L'eau tombe entre les graviers. Merci. Le banc est à nous. J'attends samedi. Le square sent l'herbe mouillée. Une cloche lointaine sonne deux fois.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,14 +1324,70 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Ava est à la cuisine. Papa accroche un calendrier.
-papa|Lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Ava reste à la maison. Elle joue avec papa. Samedi, Ava reste aussi. Dimanche encore.
-papa|Samedi et dimanche, c'est le week-end.
-narrateur|Ava touche mercredi. Elle touche samedi. Elle touche dimanche.
-papa|Mercredi, samedi, dimanche, on est à la maison.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le gravier du square sent encore la pluie.
+narrateur|Une flaque garde le ciel, tout petit.
+narrateur|Les chaînes des balançoires sont froides.
+papa|C'est mercredi, Amir.
+papa|Pas d'école.
+enfant-m|On reste au square ?
+papa|Un moment.
+papa|Samedi, on fera le pique-nique.
+enfant-m|Avec le pain ?
+papa|Avec le pain.
+papa|Samedi, c'est le week-end.
+narrateur|Amir pose la main sur le banc.
+narrateur|Le bois est mouillé, luisant.
+enfant-m|Il est froid.
+papa|La pluie est restée.
+papa|On essuie ?
+enfant-m|Oui.
+narrateur|Papa tend un linge de poche.
+narrateur|En ce moment, Amir frotte le banc.
+narrateur|L'eau part en petites traces.
+papa|Tu fais une place sèche.
+enfant-m|Pour samedi.
+papa|Pour samedi.
+papa|Et pour maintenant.
+narrateur|Ils s'assoient au bord.
+narrateur|Le gravier croque sous une chaussure.
+enfant-m|Je vois une fourmi.
+papa|Elle cherche aussi.
+narrateur|Amir suit la fourmi du doigt.
+narrateur|Elle contourne la flaque.
+papa|Mercredi, on prépare.
+papa|Samedi, on mange dehors.
+enfant-m|Et dimanche ?
+papa|Dimanche aussi, pas d'école.
+papa|Samedi et dimanche, le week-end.
+narrateur|Un oiseau secoue une branche.
+narrateur|Une goutte tombe dans la flaque.
+enfant-m|Ploc.
+papa|Tu as entendu ?
+enfant-m|Oui, papa.
+narrateur|Amir pose une feuille sur l'eau.
+narrateur|Elle flotte, puis tourne.
+papa|Un bateau.
+enfant-m|Il va au pique-nique.
+papa|Samedi, le vrai pain.
+enfant-m|Pas la feuille.
+papa|Pas la feuille.
+narrateur|Le banc sèche un peu plus.
+narrateur|Le linge est lourd d'eau.
+papa|On le tord ?
+enfant-m|Je tords.
+narrateur|L'eau tombe entre les graviers.
+papa|Merci.
+papa|Le banc est à nous.
+enfant-m|J'attends samedi.
+narrateur|Le square sent l'herbe mouillée.
+narrateur|Une cloche lointaine sonne deux fois.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,12 +1412,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Ava est à la maison le mercredi. Quels autres jours aussi ?</t>
+          <t>Quels autres jours, comme mercredi, sans l'école ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ava est à la maison le &lt;emphasis level="moderate"&gt;mercredi&lt;/emphasis&gt;. Quels autres jours aussi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Quels autres jours, comme mercredi, sans l'école ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1364,7 +1432,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>samedi | dimanche | week-end | mercredi</t>
+          <t>week-end | weekend | samedi | dimanche | le week-end | mercredi</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1421,14 +1489,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1504,10 +1572,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Ava est à la maison le mercredi. Quels autres jours aussi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Quels autres jours, comme mercredi, sans l'école ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,12 +1599,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ava a nommé mercredi. Elle a nommé samedi et dimanche. C'est le week-end.</t>
+          <t>Amir tape deux cailloux l'un contre l'autre. Samedi. Dimanche. Oui. C'est le week-end. Comme mercredi, on est ensemble. Le pain. Samedi, le pain. La flaque n'a plus de feuille. Le petit bateau a coulé. Il a fini. Le vrai pique-nique, lui, viendra. Tu as essuyé le banc. Bravo. Il est sec. Presque. Le soleil aide. Une tache claire s'élargit sur le bois.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ava a nommé &lt;emphasis level="moderate"&gt;mercredi&lt;/emphasis&gt;. Elle a nommé samedi et dimanche. C'est le week-end.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir tape deux cailloux l'un contre l'autre. Samedi. Dimanche. Oui. C'est le week-end. Comme mercredi, on est ensemble. Le pain. Samedi, le pain. La flaque n'a plus de feuille. Le petit bateau a coulé. Il a fini. Le vrai pique-nique, lui, viendra. Tu as essuyé le banc. Bravo. Il est sec. Presque. Le soleil aide. Une tache claire s'élargit sur le bois.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1600,7 +1667,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1676,10 +1743,26 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Ava a nommé mercredi. Elle a nommé samedi et dimanche. C'est le week-end.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Amir tape deux cailloux l'un contre l'autre.
+enfant-m|Samedi.
+enfant-m|Dimanche.
+papa|Oui.
+papa|C'est le week-end.
+papa|Comme mercredi, on est ensemble.
+enfant-m|Le pain.
+papa|Samedi, le pain.
+narrateur|La flaque n'a plus de feuille.
+narrateur|Le petit bateau a coulé.
+enfant-m|Il a fini.
+papa|Le vrai pique-nique, lui, viendra.
+papa|Tu as essuyé le banc.
+papa|Bravo.
+enfant-m|Il est sec.
+papa|Presque.
+papa|Le soleil aide.
+narrateur|Une tache claire s'élargit sur le bois.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,12 +1787,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le calendrier. Ava dessine un soleil.</t>
+          <t>Samedi, l'herbe est plus chaude. Papa pose la nappe près du banc. Le banc est sec. Mercredi, tu l'avais préparé. Le pain craque quand on le casse. Une miette tombe dans l'herbe. Pour la fourmi. Elle va trouver. Tu veux le bout croustillant ? Oui. Le vent soulève un coin de nappe. Amir le plaque avec la main. Merci. Dimanche, on finira les pommes. Encore le week-end. Encore le week-end. Le square sent le pain et l'herbe. La flaque n'est plus qu'un trait brillant.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa range le calendrier. Ava dessine un soleil.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Samedi, l'herbe est plus chaude. Papa pose la nappe près du banc. Le banc est sec. Mercredi, tu l'avais préparé. Le pain craque quand on le casse. Une miette tombe dans l'herbe. Pour la fourmi. Elle va trouver. Tu veux le bout croustillant ? Oui. Le vent soulève un coin de nappe. Amir le plaque avec la main. Merci. Dimanche, on finira les pommes. Encore le week-end. Encore le week-end. Le square sent le pain et l'herbe. La flaque n'est plus qu'un trait brillant.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1772,7 +1855,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1840,10 +1923,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range le calendrier. Ava dessine un soleil.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Samedi, l'herbe est plus chaude.
+narrateur|Papa pose la nappe près du banc.
+enfant-m|Le banc est sec.
+papa|Mercredi, tu l'avais préparé.
+narrateur|Le pain craque quand on le casse.
+narrateur|Une miette tombe dans l'herbe.
+enfant-m|Pour la fourmi.
+papa|Elle va trouver.
+papa|Tu veux le bout croustillant ?
+enfant-m|Oui.
+narrateur|Le vent soulève un coin de nappe.
+narrateur|Amir le plaque avec la main.
+papa|Merci.
+papa|Dimanche, on finira les pommes.
+enfant-m|Encore le week-end.
+papa|Encore le week-end.
+narrateur|Le square sent le pain et l'herbe.
+narrateur|La flaque n'est plus qu'un trait brillant.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,12 +1967,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le pique-nique est là. Samedi l'a apporté. Une miette reste dans l'herbe chaude. Le banc garde une trace sèche, claire. Le pain sent encore sous la nappe.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le pique-nique est là. Samedi l'a apporté. Une miette reste dans l'herbe chaude. Le banc garde une trace sèche, claire. Le pain sent encore sous la nappe.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1936,7 +2035,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2008,10 +2107,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|Le pique-nique est là.
+papa|Samedi l'a apporté.
+narrateur|Une miette reste dans l'herbe chaude.
+narrateur|Le banc garde une trace sèche, claire.
+narrateur|Le pain sent encore sous la nappe.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2170,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.002-02.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>square mercredi, herbe du pique-nique samedi</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ava, papa</t>
+          <t>Amir, papa</t>
         </is>
       </c>
     </row>
